--- a/Config/Excel/item.xlsx
+++ b/Config/Excel/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E151170D-CE14-49AD-A274-5DC6C90FA401}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B094F9E-EA9E-40A3-A00F-4B72E0134370}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24750" windowHeight="9885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -506,10 +506,16 @@
       <c r="A5" s="1">
         <v>200001</v>
       </c>
+      <c r="C5" s="1">
+        <v>920001</v>
+      </c>
       <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2"/>
+      <c r="F5" s="1">
+        <v>2</v>
+      </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
@@ -518,8 +524,14 @@
       <c r="A6" s="1">
         <v>200002</v>
       </c>
+      <c r="C6" s="1">
+        <v>920005</v>
+      </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -528,7 +540,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
